--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45322</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45681.37678240741</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44132</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44103</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45602</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45187</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45623.68208333333</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45447</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45441</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>44791</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45644</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45819</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44683</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44776</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44230</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>44267</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44127</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44690</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45082</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44529</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45628.6590162037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45121</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44946</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>44915</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45566</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44599</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45328</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45645.49165509259</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45615</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45229</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>45302</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45733</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44076</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44218</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>44755</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44193</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44107</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44107</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>44076</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44162</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44128</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>44259</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44285</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44434</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44675</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44676</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44216</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44864</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44209</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>44211</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44056</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44420</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44795</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>44856</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44243</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44438</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>44249</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44215</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44102</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>44221</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44151</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>44159</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44376</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44369</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44249</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44249</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44578</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44675</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>44601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>44601</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44852</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44079</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>44431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44239</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44426</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44551</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44362</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>44357</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>44574</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44588</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44455</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44462</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44574</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>44258</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44627</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>44503</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44314</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>44221</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44315</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44315</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44503</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>44874</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44502</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44712</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>44581</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44817.91766203703</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44665</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44123</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44859</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44735</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44069</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44203</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44245</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44796</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44216</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44314</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44125</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44462</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44741</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44257</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44859</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44252</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44613</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>44855</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44860</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44218</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44056</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44362</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44246</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44218</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>44412</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44272</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44218</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44753</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44802</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44844</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44305</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44069</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44214</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44781</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>44434</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44541</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44085</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44391</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44462</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44859</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44469</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44431</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44169</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44125</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44582</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44508</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44816</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44627</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44264</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44368</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44425</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44587</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44412</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44776</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44368</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44369</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44249</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>44250</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44259</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44504</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44831</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44601</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44180</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44532</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44438</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44438</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>44369</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>44742</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44481</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>44444</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>44533</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44223</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44552</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44462</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44257</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44071</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44581</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44601</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44819</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44272</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>44253</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44581</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44131</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>44678</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>44469</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44476</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44476</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44110</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>44155</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44804</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44085</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>44109</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44238</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44217</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44249</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44246</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44053</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>44053</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44642</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44067</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44160</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44463</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>44600</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44208</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44118</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>44481</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45042</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>44743</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>44774</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45149</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44362</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45744</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>44802</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45330</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>44876</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>44431</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>44987</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>44420</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>44833</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45622.56984953704</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45535</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45257</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>44536</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45362</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45422</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>44431</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45237</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45033</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44930</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44930</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45076</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>44844</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45232</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44806</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45202</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45118</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>44965</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44182</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>44595</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45233</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>44981</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45179</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44419</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44564</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44981</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45095</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45191</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>44064</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>44890</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45178</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>44125</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44315</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44887</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>44193</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>45082</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44953</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45177</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45447</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44128</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44589</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>45110</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45566</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44055</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45442</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>44228</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>44433</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45639.50075231482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44986</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45566.94976851852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>44887</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45560</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>45259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>45258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45560</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45644.69238425926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44368</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44891</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44995</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>44425</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45566</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44939</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44946</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45097</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45095</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44076</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45206</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>44165</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45566.94013888889</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>44966</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45293</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>44071</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45623.36336805556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44860</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45250</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45567</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44476</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44973</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44375</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>44434</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45341</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45293</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>44071</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45337</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44678</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45280</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44844</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44844</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44866</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44840</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45644.58818287037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45776.78690972222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45078</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>45777</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45566</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45566</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45370</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44865</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44887</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>44887</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45086</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>44551</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45167</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>44637</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45560</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44145</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45314</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45622.56041666667</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>44099</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>44161</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44161</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>44966</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44981</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>44265</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45041</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45063</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44084</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45267</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>44103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>44491</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>44103</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>44181</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45149</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>44677</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45371</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>45629.36619212963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45095</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44516</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45040</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44209</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>44236</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45428</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45447</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>44252</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44176</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45179</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>44734</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>44732</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45077</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45705</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45206</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44614</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45084</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>45456</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45174</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>44679</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45798</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45797</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44795</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45107</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45070</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45600</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>45800</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>44634</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45344</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45800</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45560</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45762</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45800</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45301</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>45762.4158912037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45095</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44172</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45082</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45209</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>44109</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>45166</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45058</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45103</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45009</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>44664</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46206,7 +46206,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45645.59553240741</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>44193</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45210</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45645.48174768518</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44165</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>44774</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45095</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>45095</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>44729</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47344,7 +47344,7 @@
         <v>45149</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45257</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45615</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45314</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48658,7 +48658,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>45002</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49062,7 +49062,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>44813</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>44833</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49367,7 +49367,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>45775.61596064815</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49600,7 +49600,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>45257</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45301</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>44966</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50624,7 +50624,7 @@
         <v>45147</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>44767</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50857,7 +50857,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45749.3887962963</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>44840</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>44817</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51157,7 +51157,7 @@
         <v>44085</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>44368</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51271,7 +51271,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>44075</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51385,7 +51385,7 @@
         <v>44383</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>44424</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>44817</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45692</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45839</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>44076</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45707</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>44119</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51928,7 +51928,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45040</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52414,7 +52414,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52476,7 +52476,7 @@
         <v>44473</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>44595</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52595,7 +52595,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45863</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45041</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53500,7 +53500,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>44834</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>44862</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>44112</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44880</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>44076</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45710</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45191</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>44782</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45831</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>44714</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45299</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45831</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45831</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54727,7 +54727,7 @@
         <v>44749</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>45845</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45846</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54970,7 +54970,7 @@
         <v>45831</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>45688.81818287037</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>44861</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45853</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45623.64486111111</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>44053</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55446,7 +55446,7 @@
         <v>44871</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55503,7 +55503,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45560</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55746,7 +55746,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55803,7 +55803,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56098,7 +56098,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56212,7 +56212,7 @@
         <v>44117</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>44267</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56388,7 +56388,7 @@
         <v>44267</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>44953</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56512,7 +56512,7 @@
         <v>44501</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>44118</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56631,7 +56631,7 @@
         <v>44817</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>44160</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56750,7 +56750,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56812,7 +56812,7 @@
         <v>44161</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>44127</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>44441</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56983,7 +56983,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57040,7 +57040,7 @@
         <v>44732</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57102,7 +57102,7 @@
         <v>44250</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>44949</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57278,7 +57278,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>44662</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>44137</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         <v>44930</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45258</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45379</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57930,7 +57930,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         <v>45021</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>45167</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>45008</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58282,7 +58282,7 @@
         <v>45210</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58344,7 +58344,7 @@
         <v>44249</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58406,7 +58406,7 @@
         <v>44616</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>44315</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58530,7 +58530,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58592,7 +58592,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58649,7 +58649,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58706,7 +58706,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>44448</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58825,7 +58825,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58882,7 +58882,7 @@
         <v>45095</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58944,7 +58944,7 @@
         <v>44079</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59001,7 +59001,7 @@
         <v>45055</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59058,7 +59058,7 @@
         <v>44995</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59120,7 +59120,7 @@
         <v>45095</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59177,7 +59177,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>45425</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>44898</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59410,7 +59410,7 @@
         <v>45177</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59529,7 +59529,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>44865</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59710,7 +59710,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59829,7 +59829,7 @@
         <v>44966</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>44914</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45681.4540625</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60067,7 +60067,7 @@
         <v>44950</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45322</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45681.37678240741</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44132</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44103</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45602</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45187</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45623.68208333333</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45447</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45441</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>44791</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45644</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45819</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44683</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44776</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44230</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>44267</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44127</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44690</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45082</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44529</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45628.6590162037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45121</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44946</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>44915</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45566</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44599</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45328</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45645.49165509259</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45615</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45229</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>45302</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45733</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44076</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44218</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>44755</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44193</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44107</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44107</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>44076</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44162</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44128</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>44259</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44285</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44434</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44675</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44676</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44216</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44864</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44209</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>44211</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44056</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44420</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44795</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>44856</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44243</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44438</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>44249</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44215</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44102</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>44221</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44151</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>44159</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44376</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44369</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44249</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44249</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44578</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44675</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>44601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>44601</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44852</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44079</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>44431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44239</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44426</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44551</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44362</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>44357</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>44574</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44588</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44455</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44462</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44574</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>44258</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44627</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>44503</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44314</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>44221</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44315</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44315</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44503</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>44874</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44502</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44712</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>44581</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44817.91766203703</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44665</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44123</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44859</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44735</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44069</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44203</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44245</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44796</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44216</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44314</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44125</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44462</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44741</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44257</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44859</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44252</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44613</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>44855</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44860</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44218</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44056</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44362</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44246</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44218</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>44412</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44272</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44218</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44753</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44802</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44844</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44305</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44069</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44214</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44781</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>44434</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44541</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44085</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44391</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44462</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44859</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44469</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44431</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44169</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44125</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44582</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44508</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44816</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44627</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44264</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44368</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44425</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44587</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44412</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44776</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44368</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44369</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44249</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>44250</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44259</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44504</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44831</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44601</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44180</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44532</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44438</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44438</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>44369</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>44742</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44481</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>44444</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>44533</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44223</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44552</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44462</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44257</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44071</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44581</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44601</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44819</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44272</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>44253</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44581</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44131</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>44678</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>44469</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44476</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44476</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44110</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>44155</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44804</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44085</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>44109</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44238</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44217</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44249</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44246</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44053</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>44053</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44642</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44067</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44160</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44463</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>44600</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44208</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44118</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>44481</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45042</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>44743</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>44774</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45149</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44362</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45744</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>44802</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45330</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>44876</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>44431</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>44987</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>44420</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>44833</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45622.56984953704</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45535</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45257</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>44536</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45362</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45422</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>44431</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45237</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45033</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44930</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44930</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45076</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>44844</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45232</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44806</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45202</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45118</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>44965</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44182</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>44595</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45233</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>44981</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45179</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44419</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44564</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44981</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45095</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45191</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>44064</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>44890</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45178</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>44125</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44315</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44887</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>44193</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>45082</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44953</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45177</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45447</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44128</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44589</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>45110</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45566</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44055</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45442</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>44228</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>44433</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45639.50075231482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44986</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45566.94976851852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>44887</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45560</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>45259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>45258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45560</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45644.69238425926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44368</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44891</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44995</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>44425</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45566</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44939</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44946</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45097</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45095</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44076</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45206</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>44165</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45566.94013888889</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>44966</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45293</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>44071</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45623.36336805556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44860</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45250</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45567</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44476</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44973</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44375</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>44434</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45341</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45293</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>44071</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45337</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44678</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45280</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44844</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44844</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44866</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44840</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45644.58818287037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45776.78690972222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45078</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>45777</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45566</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45566</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45370</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44865</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44887</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>44887</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45086</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>44551</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45167</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>44637</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45560</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44145</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45314</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45622.56041666667</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>44099</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>44161</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44161</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>44966</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44981</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>44265</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45041</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45063</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44084</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45267</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>44103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>44491</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>44103</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>44181</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45149</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>44677</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45371</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>45629.36619212963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45095</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44516</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45040</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44209</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>44236</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45428</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45447</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>44252</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44176</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45179</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>44734</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>44732</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45077</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45705</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45206</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44614</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45084</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>45456</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45174</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>44679</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45798</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45797</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44795</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45107</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45070</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45600</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>45800</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>44634</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45344</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45800</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45560</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45762</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45800</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45301</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>45762.4158912037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45095</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44172</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45082</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45209</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>44109</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>45166</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45058</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45103</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45009</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>44664</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46206,7 +46206,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45645.59553240741</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>44193</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45210</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45645.48174768518</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44165</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>44774</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45095</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>45095</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>44729</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47344,7 +47344,7 @@
         <v>45149</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45257</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45615</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45314</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48658,7 +48658,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>45002</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49062,7 +49062,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>44813</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>44833</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49367,7 +49367,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>45775.61596064815</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49600,7 +49600,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>45257</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45301</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>44966</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50624,7 +50624,7 @@
         <v>45147</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>44767</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50857,7 +50857,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45749.3887962963</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>44840</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>44817</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51157,7 +51157,7 @@
         <v>44085</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>44368</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51271,7 +51271,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>44075</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51385,7 +51385,7 @@
         <v>44383</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>44424</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>44817</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45692</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45839</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>44076</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45707</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>44119</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51928,7 +51928,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45040</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52414,7 +52414,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52476,7 +52476,7 @@
         <v>44473</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>44595</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52595,7 +52595,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45863</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45041</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53500,7 +53500,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>44834</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>44862</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>44112</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44880</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>44076</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45710</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45191</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>44782</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45831</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>44714</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45299</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45831</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45831</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54727,7 +54727,7 @@
         <v>44749</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>45845</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45846</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54970,7 +54970,7 @@
         <v>45831</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>45688.81818287037</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>44861</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45853</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45623.64486111111</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>44053</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55446,7 +55446,7 @@
         <v>44871</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55503,7 +55503,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45560</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55746,7 +55746,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55803,7 +55803,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56098,7 +56098,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56212,7 +56212,7 @@
         <v>44117</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>44267</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56388,7 +56388,7 @@
         <v>44267</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>44953</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56512,7 +56512,7 @@
         <v>44501</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>44118</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56631,7 +56631,7 @@
         <v>44817</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>44160</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56750,7 +56750,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56812,7 +56812,7 @@
         <v>44161</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>44127</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>44441</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56983,7 +56983,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57040,7 +57040,7 @@
         <v>44732</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57102,7 +57102,7 @@
         <v>44250</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>44949</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57278,7 +57278,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>44662</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>44137</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         <v>44930</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45258</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45379</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57930,7 +57930,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         <v>45021</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>45167</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>45008</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58282,7 +58282,7 @@
         <v>45210</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58344,7 +58344,7 @@
         <v>44249</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58406,7 +58406,7 @@
         <v>44616</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>44315</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58530,7 +58530,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58592,7 +58592,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58649,7 +58649,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58706,7 +58706,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>44448</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58825,7 +58825,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58882,7 +58882,7 @@
         <v>45095</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58944,7 +58944,7 @@
         <v>44079</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59001,7 +59001,7 @@
         <v>45055</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59058,7 +59058,7 @@
         <v>44995</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59120,7 +59120,7 @@
         <v>45095</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59177,7 +59177,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>45425</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>44898</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59410,7 +59410,7 @@
         <v>45177</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59529,7 +59529,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>44865</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59710,7 +59710,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59829,7 +59829,7 @@
         <v>44966</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>44914</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45681.4540625</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60067,7 +60067,7 @@
         <v>44950</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45322</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45681.37678240741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44132</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44103</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45602</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45187</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45441</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44791</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45819</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45644</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45623.68208333333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44683</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44776</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44230</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>44267</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44127</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44690</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44529</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>45121</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44915</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45229</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45566</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45302</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44599</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45733</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>45883</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45328</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44930</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45645.49165509259</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45615</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>45082</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45628.6590162037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44946</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>44076</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>44218</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>44193</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44107</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44107</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44076</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44162</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>44128</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44406</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44285</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44259</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44434</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44216</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44864</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44675</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44676</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44536</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>44209</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44211</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44420</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44795</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>44856</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44438</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44249</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>44243</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>44215</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44102</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44221</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44151</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44159</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>44376</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44369</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44249</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>44578</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44675</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44249</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>44601</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44601</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44852</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44079</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44239</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44426</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44551</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44362</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44357</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44574</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44455</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44462</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44574</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44258</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>44627</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>44503</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44314</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44315</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44315</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44221</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44874</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44502</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44551</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44712</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44581</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44817.91766203703</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44665</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44123</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44601</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44859</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44735</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44069</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44203</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44216</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44462</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44245</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44796</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>44314</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44125</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>44257</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44859</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44613</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44252</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44855</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44860</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44218</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44362</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44246</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44218</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>44412</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44218</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44272</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44753</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44802</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44844</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>44305</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44069</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44214</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44781</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>44434</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44541</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44085</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44391</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>44462</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44469</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44859</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44431</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44169</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44125</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44582</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44508</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44816</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44627</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44264</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44587</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44425</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44249</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>44831</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44504</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44259</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44180</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44601</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44369</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44532</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>44438</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44438</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44742</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44481</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44552</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44444</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44257</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>44071</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44533</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44223</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44581</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44462</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44859</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44601</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44819</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44272</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>44581</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44253</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44469</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44131</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44678</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44476</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44155</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44476</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44110</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44804</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44085</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44314</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44109</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44182</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>44238</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44249</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44067</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>44246</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>44216</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44463</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44208</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44118</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44600</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44481</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44743</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>44412</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>44776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44368</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44368</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44369</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44250</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45210</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>44713</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44930</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44165</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45566.94013888889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44844</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45232</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44966</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>44802</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45293</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>44806</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45330</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45250</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44973</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44064</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44420</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44887</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>44833</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45535</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44953</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>45257</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45447</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45341</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45293</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>44071</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45362</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44678</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45776.78690972222</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45777</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45566</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45566</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45566</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45078</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44551</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45560</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45314</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>44981</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>44265</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45041</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45063</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45086</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45267</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45566</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45040</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>44084</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>44103</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45149</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45629.36619212963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44516</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45040</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45442</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45447</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45798</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>45797</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44986</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45800</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45800</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45077</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45206</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45084</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45456</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45174</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44795</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45258</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>45258</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45260</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44634</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44891</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>44425</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45097</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45095</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45560</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>44076</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>44071</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>44172</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>44860</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>44476</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45209</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>44375</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44434</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45103</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45337</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>44664</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45280</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>44844</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>44844</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>44866</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>44840</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45644.58818287037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44656</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>45370</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44865</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>44887</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>44887</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45086</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44637</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>44193</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>44145</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45622.56041666667</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44165</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44099</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>44729</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45149</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>44161</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>44161</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45257</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44966</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45314</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45863</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44813</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>44833</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44491</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>44103</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>44181</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45257</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45301</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>44677</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>44966</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45831</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45831</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45831</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>44767</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45749.3887962963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>44817</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>44119</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45040</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>44595</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>45880.65869212963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44209</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44112</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>44236</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44782</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>45800</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44714</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45299</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44749</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45880.53909722222</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45880.55628472222</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>45428</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45881.59574074074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45688.81818287037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>44252</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>44861</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>45623.64486111111</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45839</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>44871</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40572,7 +40572,7 @@
         <v>45560</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>44176</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45883.64872685185</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45883</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45179</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45883.55503472222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45883.35074074074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45883.35534722222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>44734</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>44732</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>45853</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44117</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>45705</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45884.32354166666</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>44614</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>44267</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44267</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44953</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44501</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44118</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>44679</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>44817</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44160</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>44161</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>44127</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>44441</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45070</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>44732</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>44250</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>44949</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45600</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45344</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45301</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>44662</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45762.4158912037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45095</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>44137</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>45082</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>44109</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>44930</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45258</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45379</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45021</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45167</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45008</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45210</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45009</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44249</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>44616</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44315</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>44448</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45645.59553240741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45095</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>44079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45210</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45645.48174768518</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>44774</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45055</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>45095</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45095</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>44995</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45095</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>45425</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>44898</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>45615</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45177</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45002</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49160,7 +49160,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44865</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>44966</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>44914</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45147</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49817,7 +49817,7 @@
         <v>45681.4540625</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>44840</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>44817</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>44085</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>44368</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50169,7 +50169,7 @@
         <v>44075</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50226,7 +50226,7 @@
         <v>44383</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         <v>44424</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45692</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>44076</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45707</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>44950</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50821,7 +50821,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50940,7 +50940,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>45042</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>44473</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>45041</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>45149</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52026,7 +52026,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>45744</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52326,7 +52326,7 @@
         <v>44834</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>44862</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52574,7 +52574,7 @@
         <v>44880</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>44076</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45710</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45191</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>44987</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45622.56984953704</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45422</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45214</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>44774</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53625,7 +53625,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>45033</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53749,7 +53749,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54054,7 +54054,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54235,7 +54235,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54297,7 +54297,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45118</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>44876</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>44431</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>44536</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>44431</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55296,7 +55296,7 @@
         <v>45237</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>44981</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55482,7 +55482,7 @@
         <v>45191</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>44890</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>45178</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45076</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>44315</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>45177</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56139,7 +56139,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56201,7 +56201,7 @@
         <v>44965</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>45110</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>44182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>44595</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45233</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>44981</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45179</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>44419</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>44564</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45639.50075231482</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45095</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45566.94976851852</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>44125</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57339,7 +57339,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>44193</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45082</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57701,7 +57701,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57763,7 +57763,7 @@
         <v>44128</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57820,7 +57820,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>45644.69238425926</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>44368</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>44589</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>45566</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>44939</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>44946</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58710,7 +58710,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58767,7 +58767,7 @@
         <v>44228</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>44433</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58881,7 +58881,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58938,7 +58938,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59176,7 +59176,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59238,7 +59238,7 @@
         <v>45206</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59295,7 +59295,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>44887</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>45560</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>45259</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45560</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59595,7 +59595,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59657,7 +59657,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59714,7 +59714,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>44995</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59895,7 +59895,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>45623.36336805556</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60014,7 +60014,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         <v>45567</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60267,7 +60267,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60381,7 +60381,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60443,7 +60443,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45322</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45681.37678240741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44132</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44103</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45602</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45187</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45441</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44791</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45819</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45644</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45623.68208333333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44683</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44776</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44230</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>44267</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44127</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44690</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44529</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>45121</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44915</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45229</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45566</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45302</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44599</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45733</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>45883</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45328</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44930</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45645.49165509259</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45615</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>45082</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45628.6590162037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44946</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>44076</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>44218</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>44193</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44107</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44107</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44076</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44162</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>44128</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44406</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44285</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44259</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44434</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44216</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44864</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44675</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44676</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44536</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>44209</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44211</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44420</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44795</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>44856</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44438</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44249</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>44243</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>44215</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44102</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44221</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44151</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44159</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>44376</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44369</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44249</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>44578</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44675</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44249</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>44601</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44601</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44852</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44079</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44239</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44426</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44551</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44362</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44357</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44574</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44455</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44462</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44574</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44258</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>44627</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>44503</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44314</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44315</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44315</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44221</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44874</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44502</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44551</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44712</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44581</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44817.91766203703</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44665</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44123</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44601</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44859</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44735</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44069</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44203</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44216</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44462</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44245</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44796</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>44314</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44125</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>44257</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44859</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44613</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44252</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44855</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44860</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44218</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44362</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44246</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44218</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>44412</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44218</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44272</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44753</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44802</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44844</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>44305</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44069</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44214</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44781</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>44434</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44541</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44085</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44391</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>44462</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44469</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44859</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44431</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44169</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44125</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44582</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44508</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44816</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44627</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44264</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44587</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44425</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44249</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>44831</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44504</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44259</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44180</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44601</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44369</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44532</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>44438</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44438</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44742</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44481</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44552</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44444</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44257</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>44071</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44533</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44223</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44581</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44462</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44859</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44601</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44819</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44272</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>44581</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44253</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44469</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44131</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44678</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44476</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44155</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44476</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44110</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44804</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44085</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44314</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44109</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44182</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>44238</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44249</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44067</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>44246</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>44216</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44463</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44208</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44118</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44600</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44481</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44743</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>44412</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>44776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44368</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44368</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44369</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44250</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45210</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>44713</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44930</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44165</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45566.94013888889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44844</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45232</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44966</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>44802</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45293</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>44806</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45330</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45250</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44973</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44064</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44420</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44887</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>44833</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45535</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44953</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>45257</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45447</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45341</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45293</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>44071</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45362</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44678</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45776.78690972222</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45777</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45566</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45566</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45566</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45078</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44551</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45560</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45314</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>44981</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>44265</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45041</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45063</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45086</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45267</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45566</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45040</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>44084</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>44103</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45149</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45629.36619212963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44516</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45040</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45442</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45447</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45798</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>45797</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44986</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45800</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45800</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45077</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45206</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45084</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45456</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45174</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44795</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45258</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>45258</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45260</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44634</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44891</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>44425</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45097</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45095</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45560</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>44076</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>44071</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>44172</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>44860</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>44476</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45209</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>44375</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44434</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45103</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45337</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>44664</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45280</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>44844</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>44844</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>44866</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>44840</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45644.58818287037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44656</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>45370</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44865</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>44887</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>44887</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45086</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44637</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>44193</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>44145</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45622.56041666667</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44165</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44099</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>44729</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45149</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>44161</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>44161</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45257</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44966</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45314</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45863</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44813</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>44833</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44491</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>44103</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>44181</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45257</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45301</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>44677</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>44966</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45831</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45831</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45831</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>44767</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45749.3887962963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>44817</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>44119</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45040</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>44595</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>45880.65869212963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44209</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44112</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>44236</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44782</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>45800</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44714</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45299</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44749</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45880.53909722222</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45880.55628472222</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>45428</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45881.59574074074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45688.81818287037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>44252</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>44861</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>45623.64486111111</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45839</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>44871</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40572,7 +40572,7 @@
         <v>45560</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>44176</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45883.64872685185</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45883</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45179</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45883.55503472222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45883.35074074074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45883.35534722222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>44734</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>44732</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>45853</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44117</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>45705</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45884.32354166666</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>44614</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>44267</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44267</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44953</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44501</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44118</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>44679</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>44817</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44160</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>44161</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>44127</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>44441</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45070</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>44732</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>44250</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>44949</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45600</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45344</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45301</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>44662</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45762.4158912037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45095</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>44137</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>45082</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>44109</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>44930</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45258</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45379</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45021</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45167</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45008</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45210</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45009</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44249</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>44616</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44315</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>44448</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45645.59553240741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45095</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>44079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45210</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45645.48174768518</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>44774</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45055</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>45095</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45095</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>44995</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45095</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>45425</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>44898</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>45615</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45177</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45002</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49160,7 +49160,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44865</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>44966</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>44914</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45147</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49817,7 +49817,7 @@
         <v>45681.4540625</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>44840</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>44817</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>44085</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>44368</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50169,7 +50169,7 @@
         <v>44075</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50226,7 +50226,7 @@
         <v>44383</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         <v>44424</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45692</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>44076</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45707</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>44950</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50821,7 +50821,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50940,7 +50940,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>45042</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>44473</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>45041</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>45149</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52026,7 +52026,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>45744</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52326,7 +52326,7 @@
         <v>44834</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>44862</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52574,7 +52574,7 @@
         <v>44880</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>44076</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45710</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45191</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>44987</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45622.56984953704</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45422</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45214</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>44774</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53625,7 +53625,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>45033</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53749,7 +53749,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54054,7 +54054,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54235,7 +54235,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54297,7 +54297,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45118</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>44876</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>44431</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>44536</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>44431</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55296,7 +55296,7 @@
         <v>45237</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>44981</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55482,7 +55482,7 @@
         <v>45191</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>44890</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>45178</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45076</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>44315</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>45177</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56139,7 +56139,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56201,7 +56201,7 @@
         <v>44965</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>45110</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>44182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>44595</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45233</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>44981</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45179</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>44419</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>44564</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45639.50075231482</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45095</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45566.94976851852</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>44125</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57339,7 +57339,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>44193</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45082</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57701,7 +57701,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57763,7 +57763,7 @@
         <v>44128</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57820,7 +57820,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>45644.69238425926</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>44368</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>44589</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>45566</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>44939</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>44946</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58710,7 +58710,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58767,7 +58767,7 @@
         <v>44228</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>44433</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58881,7 +58881,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58938,7 +58938,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59176,7 +59176,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59238,7 +59238,7 @@
         <v>45206</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59295,7 +59295,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>44887</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>45560</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>45259</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45560</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59595,7 +59595,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59657,7 +59657,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59714,7 +59714,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>44995</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59895,7 +59895,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>45623.36336805556</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60014,7 +60014,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         <v>45567</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60267,7 +60267,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60381,7 +60381,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60443,7 +60443,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45322</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45681.37678240741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>44132</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45602</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45187</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>44103</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45441</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45623.68208333333</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>44791</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45644</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45819</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44683</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44776</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44230</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>44267</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44127</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44690</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44529</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45566</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45615</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44930</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45302</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45082</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45229</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45328</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44599</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>44915</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45121</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45733</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45883</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44946</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>44218</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44076</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44755</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44193</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44107</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44107</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44076</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44162</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44128</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44285</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44259</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44434</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44216</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44864</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44675</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44676</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44209</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44536</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>44211</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>44420</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44795</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>44856</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44243</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>44438</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44249</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44215</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44102</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44221</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44159</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>44151</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44376</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44369</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44249</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>44578</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>44249</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44675</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44852</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44079</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44601</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44601</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44239</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>44426</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44551</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44362</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44357</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44574</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>44462</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44455</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44574</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44258</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44627</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>44525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44503</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>44315</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44315</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44314</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44221</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>44503</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44874</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44502</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>44551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44712</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44581</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44665</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44123</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>44601</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44859</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44735</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>44455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44069</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44203</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44216</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>44462</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44245</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>44314</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>44796</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44125</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44257</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>44741</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44859</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44252</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44613</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44855</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44860</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44218</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44362</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44246</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44218</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44412</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44218</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44272</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44753</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44802</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44844</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44305</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44214</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44069</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44434</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44781</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>44541</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44085</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44391</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44462</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44469</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44431</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44169</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44125</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44582</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44508</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>44816</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>44627</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44264</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44587</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44368</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44425</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>44412</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44776</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44368</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44369</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44250</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>44713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44504</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44259</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44601</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44831</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>44180</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44438</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>44438</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>44369</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44742</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>44532</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>44481</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>44444</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>44223</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44533</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44462</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>44859</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>44552</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44071</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44257</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44601</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44581</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44819</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>44253</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>44272</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>44581</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>44469</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44131</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44678</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>44476</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44476</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44110</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44155</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>44804</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44217</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44314</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44109</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44182</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>44238</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44249</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44246</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44067</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44216</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>44642</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>44085</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44600</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44228</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>44160</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44463</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45749.3887962963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45042</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44172</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44481</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>44208</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>44118</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45078</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45258</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>44656</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45191</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>44774</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>44866</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>44743</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>44551</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45095</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45103</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45293</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45623.36336805556</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44833</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44890</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44966</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45033</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44117</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>44368</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>44677</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45299</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45301</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44362</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>44774</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45644.69238425926</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44898</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>44714</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>44209</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>44887</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>44476</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45422</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45191</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>44595</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44589</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44181</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45428</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44595</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45063</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44160</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>44420</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45097</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45077</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>44145</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44981</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45567</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45107</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44767</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45280</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45210</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45021</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45330</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45149</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>44987</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44103</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45082</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45177</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45762</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44176</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45206</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44995</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>44071</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45705</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45149</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45147</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44250</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45230</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44193</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45040</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45447</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45639.50075231482</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44085</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45095</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45095</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>44876</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44564</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45179</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>44914</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45762.4158912037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44071</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>44981</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44930</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45560</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44844</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44844</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45232</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44448</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44128</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45257</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>44939</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45566</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45777</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>44732</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45425</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45566</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45177</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45629.36619212963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45084</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>45233</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45566</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>44161</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>44161</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45149</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45566</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>45566</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44861</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45622.56041666667</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44165</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45237</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>44099</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>45371</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45456</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45095</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45095</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44749</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45167</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44383</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44930</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44782</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44817</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45267</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>44425</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44986</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45644.58818287037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>44880</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45797</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44125</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45301</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>45008</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45370</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>44678</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>44637</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>44265</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45040</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>44137</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>45710</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45337</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44084</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44501</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45560</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>45070</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>44973</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>44891</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38964,7 +38964,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45744</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45798</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44368</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>45800</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45800</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44953</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44424</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45095</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>44075</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>44817</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45086</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>44315</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41096,7 +41096,7 @@
         <v>45174</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45178</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45058</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45002</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45257</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>45206</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>44840</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>45041</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>44516</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45314</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>44165</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>44103</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45560</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45535</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>45167</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45250</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
         <v>45707</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>44930</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>44966</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>44662</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>44806</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45313,7 +45313,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>44732</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>44076</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>44076</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>44536</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44734</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45442</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>44834</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>44887</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>45258</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47289,7 +47289,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>44865</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>44076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45615</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>44953</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>45179</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47760,7 +47760,7 @@
         <v>44252</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45863</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47879,7 +47879,7 @@
         <v>44614</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>44267</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44267</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>44862</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45831</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45831</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>44109</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48608,7 +48608,7 @@
         <v>45560</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>44833</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>44441</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48789,7 +48789,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48846,7 +48846,7 @@
         <v>44887</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48903,7 +48903,7 @@
         <v>44887</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>45086</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>45831</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49250,7 +49250,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>45831</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44616</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>44817</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>44949</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>44995</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>44813</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>44865</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45118</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45166</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50383,7 +50383,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         <v>45560</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45600</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>44079</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50906,7 +50906,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51030,7 +51030,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45800</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45082</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>44236</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51687,7 +51687,7 @@
         <v>45314</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51744,7 +51744,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51863,7 +51863,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51982,7 +51982,7 @@
         <v>45881.59574074074</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52044,7 +52044,7 @@
         <v>45447</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45880.53909722222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>44729</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45880.65869212963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>44844</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45379</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45839</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45880.55628472222</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45076</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>44840</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45095</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52882,7 +52882,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45040</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>44249</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>44161</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45883.55503472222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53544,7 +53544,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53668,7 +53668,7 @@
         <v>45883.64872685185</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>45883.35074074074</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>45883.35534722222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54035,7 +54035,7 @@
         <v>45055</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54216,7 +54216,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54273,7 +54273,7 @@
         <v>44795</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54335,7 +54335,7 @@
         <v>45260</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54392,7 +54392,7 @@
         <v>45845</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>44491</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54635,7 +54635,7 @@
         <v>45041</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54754,7 +54754,7 @@
         <v>45257</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45645.59553240741</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>44871</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55173,7 +55173,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45692</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45884.32354166666</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55597,7 +55597,7 @@
         <v>45202</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>44966</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55716,7 +55716,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55778,7 +55778,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55840,7 +55840,7 @@
         <v>44119</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>44473</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>45888.44862268519</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56088,7 +56088,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56150,7 +56150,7 @@
         <v>44112</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>44127</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>45888.59415509259</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56388,7 +56388,7 @@
         <v>45344</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56445,7 +56445,7 @@
         <v>45846</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56507,7 +56507,7 @@
         <v>45888.3796875</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56569,7 +56569,7 @@
         <v>45362</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56626,7 +56626,7 @@
         <v>45341</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>44193</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>44634</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56807,7 +56807,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56988,7 +56988,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57107,7 +57107,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57169,7 +57169,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57226,7 +57226,7 @@
         <v>45209</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57340,7 +57340,7 @@
         <v>45681.4540625</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57402,7 +57402,7 @@
         <v>45883</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>45853</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>45890.84398148148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57630,7 +57630,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>44434</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57935,7 +57935,7 @@
         <v>44433</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45891.55048611111</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>45891.55418981481</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58178,7 +58178,7 @@
         <v>44664</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>44431</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>44182</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58359,7 +58359,7 @@
         <v>44981</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>44946</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58483,7 +58483,7 @@
         <v>45210</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>44679</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>44118</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58726,7 +58726,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45293</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45009</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>45095</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45110</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59316,7 +59316,7 @@
         <v>44965</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>44419</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59626,7 +59626,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59683,7 +59683,7 @@
         <v>44966</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59745,7 +59745,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59807,7 +59807,7 @@
         <v>44375</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59926,7 +59926,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59988,7 +59988,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60045,7 +60045,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60102,7 +60102,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60159,7 +60159,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>44315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45322</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45681.37678240741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44132</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44103</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45602</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45187</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45441</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44791</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45819</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44683</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44776</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44230</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44267</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44127</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44690</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>44529</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>45121</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44915</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45566</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44599</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45229</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45328</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45302</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45615</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45883</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45894.33137731482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45733</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44930</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>45082</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44946</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>44076</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44218</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44755</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44193</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44107</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>44107</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44076</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44162</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44128</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44259</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44285</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>44434</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>44216</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44864</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44675</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44676</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44536</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44209</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44211</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44420</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44795</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44856</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44243</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44438</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44249</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>44215</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44102</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44221</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44151</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44159</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44376</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>44369</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44249</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44249</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44578</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44675</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44852</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44601</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44079</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44239</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44551</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44426</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44362</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44357</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44574</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44455</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44588</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>44574</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>44258</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44627</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44525</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44503</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44315</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44315</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44314</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44221</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44503</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>44874</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>44502</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44712</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44581</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>44665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>44123</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44601</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44859</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44735</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44455</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44203</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44216</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44462</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44245</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44796</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44314</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44125</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44741</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44257</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44859</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44613</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44252</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44855</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44860</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44218</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44362</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44246</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44218</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44412</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44218</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44272</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44753</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44802</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44844</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44305</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44214</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44781</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44434</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44085</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44541</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44391</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>44462</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44469</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>44859</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>44431</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>44169</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44125</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44582</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44508</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>44816</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44627</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44587</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44264</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44425</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44249</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44368</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44369</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44250</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44713</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>44831</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44504</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44259</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>44180</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44601</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44532</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44369</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44438</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>44438</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44742</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>44552</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44257</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44481</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44581</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44533</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44223</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44462</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44859</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44272</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44581</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44601</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>44253</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44469</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44476</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44155</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44804</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44476</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44131</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44678</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44085</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44217</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44314</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44216</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44109</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44182</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44238</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44160</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44463</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>44246</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>44208</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44118</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44600</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44481</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>44743</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>44412</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44776</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44368</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>44420</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44833</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45535</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44165</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45257</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45362</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>44966</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45210</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44362</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45293</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>44930</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44930</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44844</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45330</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45232</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45250</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>44806</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44973</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45777</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44887</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45566</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>45566</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45566</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45341</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45293</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44953</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45447</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44678</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45566</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45442</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45078</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44986</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44551</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45167</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45258</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45258</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45260</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45560</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45314</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44891</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>44425</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45097</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45095</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>44981</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>44265</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44076</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45371</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45041</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45063</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45086</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>45040</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44084</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44860</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44103</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45149</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45629.36619212963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45095</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44476</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44516</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45040</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44375</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44434</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45337</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45798</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>45797</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45280</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45447</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44866</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44840</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45644.58818287037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44656</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45800</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45370</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44865</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45800</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44887</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44887</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45086</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44637</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44145</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44099</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44161</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44161</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44966</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45077</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45206</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45084</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45456</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45174</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44795</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44634</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>44491</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>44103</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44181</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44677</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45560</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45762</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44209</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>44236</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>44172</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45428</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>44252</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>44176</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45179</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45209</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>44734</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45705</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45103</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45831</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>44614</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>45831</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45831</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>44679</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>44664</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45107</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>45070</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>44193</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>45600</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>44165</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45344</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44729</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45149</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45880.65869212963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45257</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>45301</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45762.4158912037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45095</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45880.53909722222</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45880.55628472222</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45314</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45881.59574074074</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45082</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45839</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>45883.64872685185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44813</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>44833</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>45257</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>44109</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45301</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45166</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45058</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45883.55503472222</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>44966</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>45883.35074074074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45883.35534722222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45884.32354166666</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44767</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>45846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45749.3887962963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>45009</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45845</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44817</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45888.3796875</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>44119</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>45040</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45888.59415509259</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45888.44862268519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41371,7 +41371,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>44595</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45210</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45890.84398148148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>44112</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>44774</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45894.68724537037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42142,7 +42142,7 @@
         <v>45095</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>45095</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>45894.34081018518</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>44782</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45894.64597222222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45891.55048611111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45891.55418981481</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45853</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45800</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>44714</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45883</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45299</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45894.41927083334</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45615</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>44749</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45896.45008101852</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45895.67457175926</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>44861</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45002</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45898.57550925926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45863</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45681.4540625</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45898.56473379629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45898.56826388889</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>44871</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>45560</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45897</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45898.44075231482</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45898.54694444445</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>44840</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>44817</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>44085</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>44368</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>44075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>44383</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>44424</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>45692</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45707</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>44117</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>44473</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45041</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>44267</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>44267</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>44953</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>44501</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>44118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>44817</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>44834</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>44862</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>44160</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48392,7 +48392,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>44880</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>44076</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48578,7 +48578,7 @@
         <v>45710</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>44161</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>44127</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>45191</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48863,7 +48863,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>44441</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>44774</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44732</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>44250</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>44949</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>44876</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50167,7 +50167,7 @@
         <v>44431</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>44662</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50405,7 +50405,7 @@
         <v>44536</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>44137</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>44431</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50814,7 +50814,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50876,7 +50876,7 @@
         <v>44930</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>45076</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45258</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>45379</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>44965</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>44182</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45021</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>44595</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45233</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45167</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45008</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>44981</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45179</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>44419</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>44564</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45210</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>45095</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>44125</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>44249</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>44616</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>44315</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>44193</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45082</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>45230</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>44128</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53152,7 +53152,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53214,7 +53214,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>44448</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>44589</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45095</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>44228</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>44433</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>44079</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>44887</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45560</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45055</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45259</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>44995</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>45560</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45095</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54612,7 +54612,7 @@
         <v>45425</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54669,7 +54669,7 @@
         <v>44995</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>44898</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45177</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55140,7 +55140,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>44865</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55502,7 +55502,7 @@
         <v>44966</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>44914</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>44950</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>45042</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56102,7 +56102,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45149</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45744</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56397,7 +56397,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>44987</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56806,7 +56806,7 @@
         <v>45422</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45214</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57101,7 +57101,7 @@
         <v>45033</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57225,7 +57225,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57406,7 +57406,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45202</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>45118</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57706,7 +57706,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57763,7 +57763,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57820,7 +57820,7 @@
         <v>44981</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45191</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>44890</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45178</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>44315</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45177</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58420,7 +58420,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58539,7 +58539,7 @@
         <v>45110</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58658,7 +58658,7 @@
         <v>45639.50075231482</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58720,7 +58720,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58782,7 +58782,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58906,7 +58906,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59020,7 +59020,7 @@
         <v>45644.69238425926</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59082,7 +59082,7 @@
         <v>44368</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59139,7 +59139,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59201,7 +59201,7 @@
         <v>45566</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>44939</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59320,7 +59320,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59377,7 +59377,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59439,7 +59439,7 @@
         <v>44946</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59501,7 +59501,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59558,7 +59558,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59620,7 +59620,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59677,7 +59677,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>45206</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45623.36336805556</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59982,7 +59982,7 @@
         <v>45567</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60064,7 +60064,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60121,7 +60121,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60178,7 +60178,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60297,7 +60297,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45322</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45681.37678240741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44132</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44103</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45602</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45187</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45441</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44791</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45819</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44683</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44776</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44230</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44267</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44127</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44690</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>44529</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>45121</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44915</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45566</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44599</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45229</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45328</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45302</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45615</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45883</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45894.33137731482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45733</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44930</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>45082</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44946</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>44076</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44218</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44755</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44193</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44107</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>44107</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44076</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44162</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44128</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44259</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44285</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>44434</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>44216</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44864</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44675</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44676</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44536</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44209</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44211</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44420</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44795</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44856</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44243</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44438</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44249</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>44215</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44102</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44221</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44151</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44159</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44376</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>44369</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44249</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44249</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44578</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44675</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44852</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44601</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44079</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44239</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44551</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44426</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44362</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44357</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44574</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44455</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44588</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>44574</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>44258</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44627</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44525</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44503</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44315</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44315</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44314</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44221</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44503</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>44874</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>44502</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44712</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44581</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>44665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>44123</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44601</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44859</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44735</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44455</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44203</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44216</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44462</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44245</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44796</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44314</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44125</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44741</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44257</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44859</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44613</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44252</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44855</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44860</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44218</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44362</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44246</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44218</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44412</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44218</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44272</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44753</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44802</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44844</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44305</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44214</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44781</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44434</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44085</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44541</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44391</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>44462</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44469</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>44859</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>44431</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>44169</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44125</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44582</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44508</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>44816</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44627</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44587</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44264</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44425</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44249</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44368</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44369</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44250</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44713</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>44831</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44504</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44259</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>44180</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44601</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44532</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44369</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44438</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>44438</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44742</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>44552</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44257</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44481</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44581</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44533</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44223</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44462</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44859</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44272</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44581</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44601</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>44253</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44469</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44476</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44155</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44804</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44476</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44131</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44678</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44085</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44217</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44314</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44216</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44109</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44182</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44238</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44160</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44463</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>44246</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>44208</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44118</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44600</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44481</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>44743</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>44412</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44776</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44368</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>44420</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44833</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45535</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44165</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45257</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45362</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>44966</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45210</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44362</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45293</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>44930</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44930</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44844</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45330</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45232</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45250</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>44806</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44973</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45777</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44887</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45566</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>45566</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45566</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45341</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45293</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44953</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45447</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44678</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45566</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45442</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45078</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44986</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44551</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45167</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45258</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45258</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45260</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45560</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45314</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44891</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>44425</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45097</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45095</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>44981</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>44265</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44076</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45371</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45041</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45063</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45086</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>45040</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44084</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44860</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44103</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45149</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45629.36619212963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45095</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44476</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44516</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45040</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44375</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44434</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45337</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45798</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>45797</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45280</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45447</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44866</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44840</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45644.58818287037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44656</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45800</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45370</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44865</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45800</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44887</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44887</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45086</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44637</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44145</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44099</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44161</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44161</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44966</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45077</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45206</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45084</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45456</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45174</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44795</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44634</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>44491</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>44103</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44181</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44677</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45560</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45762</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44209</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>44236</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>44172</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45428</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>44252</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>44176</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45179</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45209</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>44734</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45705</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45103</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45831</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>44614</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>45831</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45831</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>44679</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>44664</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45107</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>45070</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>44193</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>45600</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>44165</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45344</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44729</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45149</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45880.65869212963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45257</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>45301</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45762.4158912037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45095</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45880.53909722222</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45880.55628472222</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45314</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45881.59574074074</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45082</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45839</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>45883.64872685185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44813</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>44833</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>45257</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>44109</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45301</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45166</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45058</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45883.55503472222</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>44966</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>45883.35074074074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45883.35534722222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45884.32354166666</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44767</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>45846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45749.3887962963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>45009</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45845</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44817</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45888.3796875</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>44119</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>45040</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45888.59415509259</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45888.44862268519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41371,7 +41371,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>44595</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45210</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45890.84398148148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>44112</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>44774</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45894.68724537037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42142,7 +42142,7 @@
         <v>45095</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>45095</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>45894.34081018518</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>44782</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45894.64597222222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45891.55048611111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45891.55418981481</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45853</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45800</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>44714</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45883</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45299</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45894.41927083334</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45615</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>44749</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45896.45008101852</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45895.67457175926</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>44861</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45002</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45898.57550925926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45863</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45681.4540625</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45898.56473379629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45898.56826388889</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>44871</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>45560</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45897</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45898.44075231482</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45898.54694444445</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>44840</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>44817</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>44085</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>44368</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>44075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>44383</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>44424</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>45692</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45707</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>44117</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>44473</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45041</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>44267</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>44267</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>44953</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>44501</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>44118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>44817</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>44834</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>44862</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>44160</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48392,7 +48392,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>44880</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>44076</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48578,7 +48578,7 @@
         <v>45710</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>44161</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>44127</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>45191</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48863,7 +48863,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>44441</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>44774</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44732</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>44250</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>44949</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>44876</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50167,7 +50167,7 @@
         <v>44431</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>44662</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50405,7 +50405,7 @@
         <v>44536</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>44137</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>44431</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50814,7 +50814,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50876,7 +50876,7 @@
         <v>44930</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>45076</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45258</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>45379</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>44965</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>44182</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45021</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>44595</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45233</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45167</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45008</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>44981</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45179</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>44419</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>44564</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45210</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>45095</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>44125</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>44249</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>44616</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>44315</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>44193</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45082</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>45230</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>44128</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53152,7 +53152,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53214,7 +53214,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>44448</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>44589</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45095</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>44228</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>44433</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>44079</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>44887</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45560</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45055</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45259</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>44995</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>45560</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45095</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54612,7 +54612,7 @@
         <v>45425</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54669,7 +54669,7 @@
         <v>44995</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>44898</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45177</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55140,7 +55140,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>44865</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55502,7 +55502,7 @@
         <v>44966</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>44914</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>44950</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>45042</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56102,7 +56102,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45149</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45744</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56397,7 +56397,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>44987</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56806,7 +56806,7 @@
         <v>45422</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45214</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57101,7 +57101,7 @@
         <v>45033</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57225,7 +57225,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57406,7 +57406,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45202</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>45118</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57706,7 +57706,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57763,7 +57763,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57820,7 +57820,7 @@
         <v>44981</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45191</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>44890</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45178</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>44315</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45177</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58420,7 +58420,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58539,7 +58539,7 @@
         <v>45110</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58658,7 +58658,7 @@
         <v>45639.50075231482</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58720,7 +58720,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58782,7 +58782,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58906,7 +58906,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59020,7 +59020,7 @@
         <v>45644.69238425926</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59082,7 +59082,7 @@
         <v>44368</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59139,7 +59139,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59201,7 +59201,7 @@
         <v>45566</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>44939</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59320,7 +59320,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59377,7 +59377,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59439,7 +59439,7 @@
         <v>44946</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59501,7 +59501,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59558,7 +59558,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59620,7 +59620,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59677,7 +59677,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>45206</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45623.36336805556</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59982,7 +59982,7 @@
         <v>45567</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60064,7 +60064,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60121,7 +60121,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60178,7 +60178,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60297,7 +60297,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45322</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45681.37678240741</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>44132</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45602</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45187</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45441</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45819</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>44791</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44683</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44776</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44230</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44267</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44127</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44690</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>44529</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45302</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45229</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45894.33137731482</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45733</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45905.44513888889</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45328</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45883</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>44915</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45121</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44599</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>44946</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45615</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45566</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>44930</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>44218</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44755</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44193</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44107</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44107</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44162</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44128</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44406</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44259</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44285</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44434</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44675</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44676</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44216</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44864</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44209</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44211</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44795</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44856</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44243</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44438</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44249</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44215</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44102</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44221</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44151</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44159</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44376</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44369</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44249</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44249</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44578</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44675</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44852</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44601</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44431</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44239</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44551</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44362</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>44357</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44574</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44455</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>44588</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>44462</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>44574</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44258</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44627</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44525</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44503</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44315</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44315</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44314</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44221</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44503</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44874</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44551</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44712</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44581</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44665</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44123</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44859</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44455</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>44735</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44203</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>44216</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>44462</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44245</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44796</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44314</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44257</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>44125</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>44741</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44859</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44613</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44252</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44860</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44218</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44362</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44246</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44412</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44218</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44272</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44218</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44753</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44802</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44844</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44305</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44214</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44781</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44434</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>44541</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>44085</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44391</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44462</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>44859</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44469</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44431</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44169</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44125</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44582</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44508</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>44816</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44264</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44627</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44587</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44425</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44249</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44504</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44259</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44831</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44180</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44601</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44532</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44438</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44438</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44369</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44742</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>44552</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44257</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44581</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44481</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>44819</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>44272</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44533</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44581</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44444</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44223</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>44462</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44859</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>44469</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44476</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44601</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44155</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>44085</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44804</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44253</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44131</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44678</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>44217</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44476</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44110</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>44314</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>44216</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>44109</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44182</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44238</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44249</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>44246</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>44642</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>44463</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44600</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44481</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44368</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>44369</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>44412</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>44476</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>44208</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>44118</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44776</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>44743</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44595</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45063</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>44250</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45097</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45258</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45147</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44656</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44145</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45230</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45040</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>44564</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45567</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>44448</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>44128</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>45257</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>44866</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45566</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45777</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45566</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45566</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>44876</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45107</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>44767</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45179</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45021</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45330</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45206</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45293</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44981</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>44930</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45705</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>44966</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45033</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44368</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>44677</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45371</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44362</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45232</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>44898</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>44939</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44732</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45425</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45177</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45629.36619212963</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44802</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45267</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45095</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45237</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>44914</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45762.4158912037</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44099</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45560</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44844</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44844</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45456</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>44749</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45167</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>44930</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>44782</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45084</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45233</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44161</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>44161</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>45149</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45566</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45566</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>45797</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>44861</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44165</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44986</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45644.58818287037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45095</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45095</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44383</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44125</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44817</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45301</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45798</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45259</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45370</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>44678</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44637</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45800</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45800</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45070</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44880</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>44973</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>44891</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45008</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44368</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44953</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44265</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45040</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44817</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44137</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
         <v>45710</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>45337</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>44084</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45174</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44501</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45560</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45744</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45314</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44165</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>45560</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>44424</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45831</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45831</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45535</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45831</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45831</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>45095</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>44950</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45250</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>45881.59574074074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45880.53909722222</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45880.65869212963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45839</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>45880.55628472222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>44315</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45883.55503472222</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44860</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45883.64872685185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>45883.35074074074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45883.35534722222</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45845</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>44966</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>44806</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45884.32354166666</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>45888.44862268519</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45888.59415509259</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45888.3796875</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45890.84398148148</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45891.55048611111</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45891.55418981481</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45894.68724537037</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45895.67457175926</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45178</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45894.64597222222</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45894.34081018518</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45894.41927083334</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45896.45008101852</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45058</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45002</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45898.56473379629</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45898.56826388889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45898.44075231482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45897</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45898.54694444445</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>45898.57550925926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40120,7 +40120,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>45903.60679398148</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45853</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>45903.62509259259</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>45903.59841435185</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         <v>45903.60240740741</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>45902.62799768519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>45902.63649305556</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45903.59527777778</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45904.58920138889</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41030,7 +41030,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45257</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45206</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>44834</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>45800</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45905.42600694444</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45905.32633101852</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45905.32957175926</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45258</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>44840</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45041</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>44865</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44516</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>44953</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>45179</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>45905.47065972222</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>44103</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>45904.62306712963</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>45905.45561342593</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45905.33390046296</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45681.4540625</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45863</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45905.35103009259</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>45883</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>44862</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>44109</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>45560</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>45707</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>44887</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>44887</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45086</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>44930</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>44662</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>44616</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>44732</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>44949</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>44813</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44536</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44734</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>45442</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>44887</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45560</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45615</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>44252</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>44614</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45899,7 +45899,7 @@
         <v>44267</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>44267</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>44833</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44441</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>44817</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>44865</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45118</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44236</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46737,7 +46737,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46856,7 +46856,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>45166</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45447</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44729</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44844</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45076</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45095</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47513,7 +47513,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45600</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45082</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>44795</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45260</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>44491</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
         <v>45041</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44871</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>45692</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45379</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48998,7 +48998,7 @@
         <v>44840</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44966</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44249</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>44161</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45210</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49779,7 +49779,7 @@
         <v>44127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>45055</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45341</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50198,7 +50198,7 @@
         <v>44193</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>44431</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>44119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44473</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>44182</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>44981</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44112</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45344</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45362</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>44679</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44634</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>44118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>45209</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>45293</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52278,7 +52278,7 @@
         <v>44434</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>44433</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>45214</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45110</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>44664</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52759,7 +52759,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52883,7 +52883,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>44966</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>44946</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45210</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45078</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>45191</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>44551</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>45009</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>44833</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>44890</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53783,7 +53783,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53840,7 +53840,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53897,7 +53897,7 @@
         <v>45095</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>44117</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>44965</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45299</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>44419</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54373,7 +54373,7 @@
         <v>45301</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54435,7 +54435,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54554,7 +54554,7 @@
         <v>44375</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54616,7 +54616,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54678,7 +54678,7 @@
         <v>45644.69238425926</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54740,7 +54740,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54859,7 +54859,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         <v>44714</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54973,7 +54973,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45258</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>44209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>44315</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55687,7 +55687,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>44228</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55863,7 +55863,7 @@
         <v>44887</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55920,7 +55920,7 @@
         <v>45422</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55977,7 +55977,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>45042</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>44172</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>45191</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56272,7 +56272,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>44595</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56505,7 +56505,7 @@
         <v>44589</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56562,7 +56562,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56624,7 +56624,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56686,7 +56686,7 @@
         <v>44774</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45095</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>44160</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45623.36336805556</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57105,7 +57105,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57162,7 +57162,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57281,7 +57281,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>44774</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45149</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>44181</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45428</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58243,7 +58243,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45762</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58419,7 +58419,7 @@
         <v>44176</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58719,7 +58719,7 @@
         <v>44431</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>44420</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58833,7 +58833,7 @@
         <v>45149</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58947,7 +58947,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -59004,7 +59004,7 @@
         <v>45077</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59066,7 +59066,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         <v>44250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59190,7 +59190,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59252,7 +59252,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59309,7 +59309,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59366,7 +59366,7 @@
         <v>44193</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59428,7 +59428,7 @@
         <v>44981</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59490,7 +59490,7 @@
         <v>45447</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59552,7 +59552,7 @@
         <v>44085</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59666,7 +59666,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59780,7 +59780,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59842,7 +59842,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>45095</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59961,7 +59961,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -60023,7 +60023,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60147,7 +60147,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45210</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>44987</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60561,7 +60561,7 @@
         <v>44103</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>45082</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60804,7 +60804,7 @@
         <v>45177</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>44995</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45322</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45681</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44132</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44103</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45602</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45187</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45441</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44791</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45819</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44683</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44776</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44230</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44267</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44127</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44690</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44529</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>45121</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44915</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45566</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44599</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45229</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45302</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45328</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45615</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45894.33137731482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44930</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45883</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45905.44513888889</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45733</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45082</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>44946</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>44218</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44755</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44193</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44107</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44107</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44162</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44128</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44406</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44285</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44434</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44675</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44676</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44536</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44259</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44216</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44864</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44209</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44211</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44420</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44795</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44856</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44215</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44243</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44438</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44249</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44102</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44221</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44151</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44159</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44376</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44369</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44578</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44249</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44249</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44675</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44852</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44601</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44431</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44239</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44551</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44426</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44362</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>44357</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44574</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44462</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>44455</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44588</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>44574</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44258</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44627</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44525</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44315</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44315</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44314</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44221</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44503</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44503</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44874</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44551</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44712</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44581</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44665</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44123</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44601</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44859</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44455</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>44203</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44216</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44462</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>44245</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44796</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>44735</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44314</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44125</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44741</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44257</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44859</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44613</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44252</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44860</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44218</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44362</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44246</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44218</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44412</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44218</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44272</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44753</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44802</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44844</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44214</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44305</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44781</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44434</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>44541</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>44391</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44462</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>44469</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44431</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44169</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44125</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44582</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44508</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>44816</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>44627</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44264</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44587</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44425</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44249</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44250</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44713</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44831</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44259</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44504</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>44368</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>44369</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>44180</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44369</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>44532</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44481</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>44533</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44601</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44552</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>44257</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44581</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44272</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44601</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44131</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44581</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>44678</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>44469</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>44476</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>44438</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>44438</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44742</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>44155</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44804</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>44109</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44182</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44238</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44444</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44217</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>44249</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>44246</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>44642</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44223</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>44216</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>44160</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44463</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44462</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44859</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>44208</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44118</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44743</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44420</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>44833</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>44253</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45535</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45257</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45362</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45210</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44930</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>44930</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44362</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44844</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45232</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44802</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>44806</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45330</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44165</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>44966</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45293</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44476</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44887</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44953</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44973</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45447</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45341</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45777</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45566</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45566</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45566</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45566</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44678</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44314</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45442</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45078</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44551</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>44986</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45167</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45560</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45314</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45258</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45260</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>44981</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>44265</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45267</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44891</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45041</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45063</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45086</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44425</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45040</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>45097</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45095</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45371</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44103</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>45149</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>44860</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45095</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>44600</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>44516</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45040</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>44476</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>44481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44375</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>44434</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45447</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44412</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45337</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45280</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45798</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44844</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44844</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44866</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44840</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45797</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>44776</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>44656</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45370</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44865</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45800</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45077</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45800</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44887</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44887</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>45206</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45084</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45086</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45456</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45174</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44637</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44145</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44795</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44099</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>44634</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44161</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44161</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44966</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>45560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45762</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44491</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44103</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44172</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>44181</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>44677</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>45209</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45103</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>44209</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44236</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44664</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45428</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>44193</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44252</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>44165</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44176</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45179</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45149</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45257</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>44734</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>44732</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45314</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45831</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45705</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>45831</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>44614</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>44679</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>44813</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>44833</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45107</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45070</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45880.65869212963</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45600</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45344</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45257</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45301</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>44966</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45301</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45095</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44767</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>45880.53909722222</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45880.55628472222</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>45082</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>44109</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45166</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45058</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44817</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>44119</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45040</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45881.59574074074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>44595</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45009</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45210</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45839</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>44774</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45095</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45095</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>44112</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>44782</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45615</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44714</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>45883.64872685185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45002</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45299</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>44749</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45147</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44840</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44817</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45883.55503472222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>44368</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>44383</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44424</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45692</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45707</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>44473</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>44861</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45041</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43013,7 +43013,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45883.35074074074</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45883.35534722222</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44834</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>44862</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>44880</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45710</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45191</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>44774</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>44871</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45560</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>44876</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>44431</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>44536</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>44431</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45237</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45076</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44965</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>44182</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44595</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45233</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45884.32354166666</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>44981</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>45179</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>44419</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>44564</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45095</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45846</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>44125</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>44193</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45082</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>44117</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>44128</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>44589</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>44267</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>44267</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>44953</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>44228</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>44433</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45845</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44501</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45888.3796875</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>44887</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45888.59415509259</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44817</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45888.44862268519</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45560</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>44160</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45560</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>44161</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>44127</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>44441</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>44995</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>44732</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45890.84398148148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44250</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>44949</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45894.68724537037</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50163,7 +50163,7 @@
         <v>45894.34081018518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50344,7 +50344,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45894.64597222222</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45891.55048611111</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45891.55418981481</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45894.41927083334</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44662</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50825,7 +50825,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50939,7 +50939,7 @@
         <v>45896.45008101852</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45895.67457175926</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>44137</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45898.57550925926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45898.56473379629</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45898.56826388889</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>44930</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45258</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45379</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52057,7 +52057,7 @@
         <v>45897</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>45898.44075231482</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45021</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45898.54694444445</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45008</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45902.62799768519</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45902.63649305556</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45210</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>44249</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>44616</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>44315</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45230</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45904.62306712963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>45903.59527777778</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>44448</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45883</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45853</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45904.58920138889</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45903.60679398148</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45903.59841435185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45095</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53733,7 +53733,7 @@
         <v>45903.60240740741</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>45903.62509259259</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45800</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53981,7 +53981,7 @@
         <v>45831</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45863</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45908.56493055556</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45905.35103009259</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45905.42600694444</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45905.45561342593</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>44995</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>45905.32633101852</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45905.32957175926</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>45905.33390046296</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         <v>45095</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54700,7 +54700,7 @@
         <v>45905.47065972222</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54762,7 +54762,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>45425</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>45681</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>44898</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45177</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55233,7 +55233,7 @@
         <v>44865</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>44966</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55595,7 +55595,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>44914</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>45831</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>44950</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45042</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         <v>45149</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56485,7 +56485,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45744</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56661,7 +56661,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>44987</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45422</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>45214</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57246,7 +57246,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45033</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57613,7 +57613,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57675,7 +57675,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>45202</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>45118</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57913,7 +57913,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>44981</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45191</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58208,7 +58208,7 @@
         <v>44890</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58265,7 +58265,7 @@
         <v>45178</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>44315</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58384,7 +58384,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45177</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58565,7 +58565,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58746,7 +58746,7 @@
         <v>45110</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58927,7 +58927,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59165,7 +59165,7 @@
         <v>44368</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>45566</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>44939</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59403,7 +59403,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59522,7 +59522,7 @@
         <v>44946</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59641,7 +59641,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59703,7 +59703,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>45206</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59941,7 +59941,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -60003,7 +60003,7 @@
         <v>45567</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60318,7 +60318,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60380,7 +60380,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45322</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45681</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44132</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44103</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45602</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45187</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45441</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44791</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45819</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44683</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44776</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44230</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44267</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44127</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44690</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44529</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>45121</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44915</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45566</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44599</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45229</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45302</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45328</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45615</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45894.33137731482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44930</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45883</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45905.44513888889</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45733</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45082</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>44946</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>44218</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44755</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44193</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44107</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44107</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44162</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44128</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44406</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44285</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44434</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44675</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44676</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44536</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44259</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44216</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44864</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44209</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44211</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44420</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44795</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44856</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44215</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44243</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44438</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44249</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44102</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44221</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44151</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44159</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44376</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44369</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44578</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44249</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44249</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44675</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44852</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44601</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44431</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44239</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44551</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44426</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44362</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>44357</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44574</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44462</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>44455</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44588</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>44574</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44258</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44627</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44525</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44315</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44315</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44314</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44221</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44503</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44503</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44874</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44551</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44712</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44581</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44665</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44123</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44601</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44859</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44455</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>44203</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44216</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44462</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>44245</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44796</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>44735</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44314</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44125</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44741</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44257</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44859</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44613</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44252</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44860</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44218</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44362</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44246</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44218</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44412</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44218</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44272</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44753</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44802</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44844</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44214</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44305</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44781</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44434</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>44541</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>44391</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44462</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>44469</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44431</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44169</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44125</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44582</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44508</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>44816</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>44627</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44264</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44587</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44425</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44249</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44250</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44713</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44831</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44259</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44504</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>44368</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>44369</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>44180</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44369</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>44532</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44481</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>44533</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44601</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44552</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>44257</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44581</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44272</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44601</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44131</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44581</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>44678</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>44469</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>44476</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>44438</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>44438</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44742</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>44155</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44804</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>44109</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44182</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44238</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44444</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44217</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>44249</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>44246</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44704.93234953703</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44564.47854166666</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>44642</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44223</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>44216</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44659.55756944444</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>44160</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44463</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44462</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44859</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>44208</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44118</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44743</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45617.58458333334</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44420</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>44833</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>44253</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45535</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44770.56407407407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45257</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45541.55064814815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45362</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45618.69439814815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>44816.75416666667</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45374.71145833333</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45210</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44754.60368055556</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44930</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>44930</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44362</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44844</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45232</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44802</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44817.92298611111</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>44806</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45735.29822916666</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45042.48407407408</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45357.58004629629</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45330</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>44778.47692129629</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44165</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>44816.75733796296</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>44966</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45744.38512731482</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45744.38790509259</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45293</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45770.59953703704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45770.60439814815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45391.42537037037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45639.34571759259</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45749.42486111111</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45639.42581018519</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45709.44688657407</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45252.50694444445</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45566.43896990741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45566.44668981482</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45740.35782407408</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44476</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44887</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45103.52126157407</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44949.59946759259</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45232.79605324074</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44953</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44973</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45609.64965277778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45447.58180555556</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45447</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>44922.43804398148</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45103.91359953704</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45341</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45777</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45391.43108796296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45754.63559027778</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45322.49793981481</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45566</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45566</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45566</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45566</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44678</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45002.7171875</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44314</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45442</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45530.93302083333</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44767.83413194444</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45078</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44993.91690972223</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>45560.60784722222</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45133.57666666667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44551</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>44986</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>44957.84447916667</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45167</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45560</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44937.78541666667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45314</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45258</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45260</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45250.59774305556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>44981</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>44265</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45323.56947916667</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45593.66155092593</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45267</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44891</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45041</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45063</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45086</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45530.92288194445</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>44897.4424537037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45113.58054398148</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45601.78827546296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44425</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45040</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45727.27097222222</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45020.87799768519</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>45593.48171296297</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45593.48603009259</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45551.63465277778</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>45097</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45095</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>45463.79559027778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45371</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44103</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45068.539375</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>45149</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45617.65668981482</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45302.47346064815</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>44622.45858796296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45293.64920138889</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>44860</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44564.68190972223</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>44958.93928240741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45328.44785879629</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45095</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>44600</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>44516</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45040</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45792.37668981482</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45467.48385416667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>44476</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45615.33805555556</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>44481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45796.4444212963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44375</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45796.45342592592</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>44434</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45447</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45639.38251157408</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45609.65366898148</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45572.48486111111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45554.2862037037</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44412</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45337</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45316.62950231481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45797.5184375</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45551.56912037037</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45428.45214120371</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45428.4608912037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45280</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45798</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45797.5658912037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44844</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44844</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44866</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44840</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45797.60138888889</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45797</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45702.36035879629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45735.29954861111</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45607.76170138889</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>45800.57334490741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>44776</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>44656</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>44622.47993055556</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45631.69237268518</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45719.49388888889</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45370</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44865</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45800</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45077</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45800</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45800.58203703703</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44887</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44887</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>45206</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45084</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45086</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45456</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45174</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45629.35886574074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45740.3552199074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45645.56427083333</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44637</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45692.54231481482</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44145</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45642.36315972222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44795</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45624.58550925926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44099</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45805.86400462963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45096.42861111111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45805.8593287037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45715.74398148148</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>44634</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45629.34311342592</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45622.4261574074</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45622.42899305555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44161</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44161</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44966</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>45560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45762.53134259259</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45762</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44964.43262731482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45604.49379629629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>44966.74208333333</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45810.67283564815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45516.53788194444</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45554.27943287037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45812.63094907408</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44491</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44103</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44172</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45812.47408564815</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45812.3731712963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>44181</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45572.67354166666</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>45692.55859953703</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45812.40525462963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>44677</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45147.46668981481</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45639.4240162037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45817.46142361111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45554.69748842593</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45209.00003472222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>45209</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45184.53783564815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45639.34060185185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45639.34267361111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45723.48126157407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45817.41699074074</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45817.44313657407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45243.44707175926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45660.58204861111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45103</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>44209</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>45819.47800925926</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45819.37645833333</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45700.3816087963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44236</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45819.38228009259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45253.57049768518</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45566.5353125</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>45555.39886574074</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>45678.64803240741</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45820.64690972222</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45820.66185185185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45820.47420138889</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45604.50295138889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44664</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45274.65848379629</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>45740.56240740741</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44767.83041666666</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45428</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45229.61754629629</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45720.36722222222</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45824.6362037037</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45824.68121527778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>44735.48800925926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45824.64903935185</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45824.65921296296</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>44193</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44252</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45825.65684027778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45826.61688657408</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>44165</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44176</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45343.57483796297</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45441.57834490741</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45441.59644675926</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>44964.5900462963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45179</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45149</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45257</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45698.46657407407</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>44734</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>44732</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45832.67672453704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45314</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>45308.87994212963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45831</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>44823.31814814815</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45705</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45623.659375</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45006.8075925926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45740.48041666667</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>45831</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>44614</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45426.26847222223</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>44679</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>44813</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>44833</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45468.57454861111</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45719.49042824074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>44725.56457175926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45604.47024305556</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>44467.94783564815</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44653.50954861111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45379.54880787037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45107</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45415.83293981481</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45070</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45880.65869212963</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45600</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45279.46747685185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45421.53177083333</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45421.53583333334</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45344</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45257.45836805556</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45835.61672453704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45257</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45301</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45302.48125</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>44966</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>45727.61766203704</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>45838.66701388889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45301</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45095</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44767</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45609.65891203703</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>45880.53909722222</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45880.55628472222</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>45086.56109953704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>45082</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45840.35300925926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44903.69664351852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45840.37001157407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>44109</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45166</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45058</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45075.71163194445</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45680.36810185185</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44817</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>44119</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45040</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45639.38752314815</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45235.45121527778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45644.94405092593</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45881.59574074074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45840.56216435185</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45665.41304398148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>44595</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45009</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45096.42487268519</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45516.5593287037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45142.55728009259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45616.27108796296</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45616.28719907408</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45593.50768518518</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45646.4853125</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45210</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45712.48190972222</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>45636.3790162037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45839</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>44774</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45095</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45095</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45728.42060185185</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45009.38880787037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>44112</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45084.81885416667</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45631.72401620371</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>44782</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45615</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45698.80957175926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>44973.5909375</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45687.45034722222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44714</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>45883.64872685185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45002</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45530.94261574074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45299</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45713.4383912037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45320.70833333334</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>44749</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45744.33431712963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45147</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>44759.65983796296</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45520.56111111111</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44840</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44817</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45883.55503472222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>44368</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44369.24979166667</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>44383</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44424</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45692</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45707</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45688.46846064815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45709.58696759259</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44476.24972222222</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44992.49708333334</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>44473</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>44820.59762731481</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45705.55550925926</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45705.55886574074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>44613.45770833334</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>44861</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45749.3371875</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45041</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45082.66623842593</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43013,7 +43013,7 @@
         <v>45719.63878472222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>44987.51744212963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45883.35074074074</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45883.35534722222</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45688.46208333333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>45660.57175925926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44834</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>44862</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>44973.41844907407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>44880</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45710</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45775.6037037037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45191</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45740.48484953704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>44774</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45770.45534722223</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45770.46763888889</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45236.37188657407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45236.37878472222</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>44879.75650462963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>44871</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45070.69009259259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>44886.42974537037</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45070.58025462963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>44526.39090277778</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45560</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45566.32579861111</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45042.60699074074</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44914.75953703704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45728.36512731481</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>44876</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>44431</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>44642.39262731482</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>44536</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45735.64335648148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45735.6669212963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>44431</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45237</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45428.48278935185</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45548.58607638889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45076</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45735.67384259259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44965</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45681.64767361111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>44944.42813657408</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>45754.46591435185</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>44182</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44595</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45233</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45562.40121527778</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45763.32456018519</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45884.32354166666</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>44981</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45086.56525462963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>45179</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>44503.48954861111</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>44419</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>44564</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>45566.53284722222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45095</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45636.85886574074</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45846</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>44125</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>44193</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45082</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45082.65296296297</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45082.66013888889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45846.37765046296</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>44117</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45013.44790509259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>44128</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45629.6427662037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>45846.38990740741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>44589</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>44607.28710648148</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>44900.72767361111</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>44267</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>44267</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45845.59033564815</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>44953</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>45740.47725694445</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>44228</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>44433</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45845</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44501</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>45845.6499537037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45888.3796875</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45357.56899305555</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45723.47864583333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>44887</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45888.59415509259</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44817</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45888.44862268519</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45560</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>44160</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45560</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45523.55290509259</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>44161</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>44127</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45463.79037037037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>44441</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>44995</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>44867.47490740741</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45677.65697916667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45103.51917824074</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>44732</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45890.84398148148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44250</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>44949</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45113.7019212963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>44993.89005787037</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>44949.55903935185</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
         <v>44949.5928587963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45894.68724537037</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50163,7 +50163,7 @@
         <v>45894.34081018518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>44960.61972222223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50344,7 +50344,7 @@
         <v>45776.7610300926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45894.64597222222</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45891.55048611111</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45891.55418981481</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45894.41927083334</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44662</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45853.9731712963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45853.97888888889</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50825,7 +50825,7 @@
         <v>45853.96457175926</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>45853.98606481482</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50939,7 +50939,7 @@
         <v>45896.45008101852</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45555.45396990741</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>44918.41450231482</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45895.67457175926</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>44137</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45622.59552083333</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45898.57550925926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45854.89873842592</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45898.56473379629</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45898.56826388889</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45855.89788194445</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45854.89011574074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45855.65826388889</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>44930</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45258</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45379</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45621.5675462963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45621.58040509259</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45260.37900462963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52057,7 +52057,7 @@
         <v>45897</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>45898.44075231482</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45855.92417824074</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45021</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45898.54694444445</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45008</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45902.62799768519</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45902.63649305556</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45523.54790509259</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45210</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>44249</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>44616</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>44315</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45593.49458333333</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>44550.79950231482</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45230</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>45013.45861111111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45904.62306712963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>45903.59527777778</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>44448</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45883</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45853</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45554.31143518518</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45904.58920138889</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45903.60679398148</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45903.59841435185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45095</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53733,7 +53733,7 @@
         <v>45903.60240740741</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>45903.62509259259</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45800</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45709.57898148148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53981,7 +53981,7 @@
         <v>45831</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45863</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45908.56493055556</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45905.35103009259</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45905.42600694444</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45905.45561342593</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>44995</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>45905.32633101852</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45905.32957175926</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>45905.33390046296</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         <v>45095</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54700,7 +54700,7 @@
         <v>45905.47065972222</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54762,7 +54762,7 @@
         <v>45636.85606481481</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>45425</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>45681</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>44898</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>45586.55983796297</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45177</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>45456.42511574074</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45631.68104166666</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55233,7 +55233,7 @@
         <v>44865</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45664.4512962963</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>45680.37934027778</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>44980.33758101852</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>45870.50287037037</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>44966</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55595,7 +55595,7 @@
         <v>45820.62386574074</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>44914</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>45870.4994212963</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>45831</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>44974.72851851852</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>44950</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>45601.54071759259</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>45323.61266203703</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45181.79957175926</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45042</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45681.56399305556</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45257.48733796296</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45225.94203703704</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45082.57385416667</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         <v>45149</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56485,7 +56485,7 @@
         <v>45706.64918981482</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45744</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45446.48325231481</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56661,7 +56661,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>45664.45697916667</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>44993.61875</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>45698.48292824074</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>44987</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>45247.62015046296</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45422</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>45214</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>45421.52635416666</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>45420.63292824074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57246,7 +57246,7 @@
         <v>45125.57719907408</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45033</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45621.55528935185</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45103.52680555556</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45688.46606481481</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>45022.59966435185</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57613,7 +57613,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57675,7 +57675,7 @@
         <v>45267.45017361111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>45202</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>45118</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45629.40020833333</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57913,7 +57913,7 @@
         <v>45225.92840277778</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>44900.723125</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>44981</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>44922.47258101852</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45191</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58208,7 +58208,7 @@
         <v>44890</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58265,7 +58265,7 @@
         <v>45178</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>44315</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58384,7 +58384,7 @@
         <v>45762.41467592592</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45177</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45623.6296875</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58565,7 +58565,7 @@
         <v>45639.42065972222</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45197.3700462963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45264.60973379629</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58746,7 +58746,7 @@
         <v>45110</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>45008.59934027777</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45594.30484953704</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58927,7 +58927,7 @@
         <v>45593.60833333333</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>45604.48474537037</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>44942.70369212963</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>44617.43332175926</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59165,7 +59165,7 @@
         <v>44368</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>45660.58243055556</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>45566</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>44939</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59403,7 +59403,7 @@
         <v>45202.50096064815</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45693.47490740741</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59522,7 +59522,7 @@
         <v>44946</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         <v>45706.64829861111</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59641,7 +59641,7 @@
         <v>45082.64861111111</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59703,7 +59703,7 @@
         <v>45299.38380787037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>45720.37665509259</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>45250.57002314815</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>45206</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59941,7 +59941,7 @@
         <v>44964.6525925926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -60003,7 +60003,7 @@
         <v>45567</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45607.76746527778</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45607.77384259259</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>44490.22488425926</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45754.66113425926</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60318,7 +60318,7 @@
         <v>45565.32090277778</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60380,7 +60380,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -567,7 +567,7 @@
         <v>44278</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>45664.66346064815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44624</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>44897</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44599</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>44777</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>45322</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45664.45395833333</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44888</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45693.47141203703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45238.63822916667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45681</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44369</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44425</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45723.36914351852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>44103</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44132</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45681.36553240741</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45602</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>45707.57879629629</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45723.49467592593</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>45187</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>44690</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45267.39979166666</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45447</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45441</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45477.60511574074</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>44791</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45819</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>44903.44127314815</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44683</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44776</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44230</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44267</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>44127</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44529</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45719.56197916667</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45302</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44622.45375</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45082</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45800.56177083333</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45149.57418981481</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45425.47636574074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45601.67776620371</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45229</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>45555.54835648148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45328</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45723.63261574074</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>44915</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44599</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45121</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>45546.6384375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45555.42803240741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45684.6628587963</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44946</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45894.33137731482</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>45905.32633101852</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>45905.44513888889</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45566</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45615</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>44930</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>45880.66829861111</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45733</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45883</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44218</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44755</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44193</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>44107</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44107</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44162</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44128</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44406</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44285</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44259</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>44434</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44216</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>44675</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44676</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44864</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44600.72219907407</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44209</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44824.88344907408</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44211</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44799.66334490741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>44420</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44795</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44438</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>44249</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>44856</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>44243</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44215</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44102</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44221</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>44151</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>44159</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44376</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44369</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44249</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44578</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44675</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44249</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44852</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44601</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>44601</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>44431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44426</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44239</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44551</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44362</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44357</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44525.84820601852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44588</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44574</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44455.4068287037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44455</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44462</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44889.57587962963</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44574</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>44627</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>44525</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44503</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>44314</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44258</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44221</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44315</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44315</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44874</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44502</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44712</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>44123</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44833.56607638889</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44581</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44601</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>44665</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44859</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44672.98665509259</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44735</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44203</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44216</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44462</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>44245</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>44796</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44782.5928587963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44314</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>44368.99104166667</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44257</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>44741</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44125</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44460.97055555556</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44859</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44678.86717592592</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44613</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44252</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44855</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44887.488125</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44860</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>44218</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44362</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44246</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>44412</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>44218</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44218</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44272</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44753</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44802</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44844</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>44305</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44214</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44214.36115740741</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44434</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>44781</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44564.46180555555</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44541</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44391</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>44313.50966435186</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>44462</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44859</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>44469</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>44294.74578703703</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>44431</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44595.73182870371</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44169</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44125</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44582</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44508</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44656.51680555556</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44816</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44627</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44264</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44587</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44434.64474537037</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>44425</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>44820.58339120371</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44365.70483796296</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44368</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44369</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44249</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44504</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>44831</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44180</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>44601</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>44532</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44369</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>44438</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>44438</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>44742</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>44552</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44879.75467592593</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44257</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44444</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44581</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>44588.61754629629</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44132.63935185185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44223</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>44462</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44819</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>44859</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44250</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>44272</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>44581</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>44630.64725694444</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>44469</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>44253</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>44713</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>44476</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>44155</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44804</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44875.96684027778</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44476</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44110</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>44217</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44259</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44314</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44697.38225694445</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44160</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44463</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>44208</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>44118</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44216</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>44600</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>44743</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>44481</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>44635.71011574074</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44412</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44776</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44368</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44368.96609953704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44425.69079861111</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>44468.75822916667</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45147</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44362</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45315.48575231482</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45275.41934027777</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44564</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45744.3828125</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>44898</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45407.04653935185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44966.73841435185</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>45071.47526620371</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>44448</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>44128</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45257.43741898148</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45257</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45770.46248842592</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>44966.74954861111</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44802</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45566</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45777</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45230</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45744.48476851852</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45566</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44476</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>44897.571875</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>44672.99238425926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45566</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45735.69887731481</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45736.38344907408</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>44595</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44876</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45727.40373842593</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>44481</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45179.86133101852</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45179</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45709.38167824074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45783.564375</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44918.42355324074</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45097</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45735.29673611111</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>45309.56436342592</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45309.58428240741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45309.60451388889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45086.43366898148</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44915.58520833333</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44533</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45642.82921296296</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>44145</v>
       </c>
       <c r="